--- a/Регулятор давления РДГ-50Н(В).xlsx
+++ b/Регулятор давления РДГ-50Н(В).xlsx
@@ -7,8 +7,8 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="28620" windowHeight="13020"/>
   </bookViews>
   <sheets>
-    <sheet name="РДГ-50Н(В) седло 25 мм" sheetId="3" r:id="rId1"/>
-    <sheet name="РДГ-50Н(В) седло 35 мм" sheetId="4" r:id="rId2"/>
+    <sheet name="РДГ-50Н(В) седло 35 мм" sheetId="4" r:id="rId1"/>
+    <sheet name="РДГ-50Н(В) седло 25 мм" sheetId="3" r:id="rId2"/>
     <sheet name="РДГ-50Н(В) седло 42 мм" sheetId="5" r:id="rId3"/>
   </sheets>
   <calcPr calcId="144525"/>
@@ -300,6 +300,21 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -320,21 +335,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -611,16 +611,15 @@
   <dimension ref="A1:M17"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="33.5546875" customWidth="1"/>
-    <col min="2" max="2" width="38.109375" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="21" customHeight="1">
+    <row r="1" spans="1:13" ht="22.95" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -634,29 +633,29 @@
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
     </row>
-    <row r="2" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A2" s="21" t="s">
+    <row r="2" spans="1:13" ht="19.5" customHeight="1">
+      <c r="A2" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
-      <c r="J2" s="19"/>
-      <c r="K2" s="19"/>
-      <c r="L2" s="19"/>
-      <c r="M2" s="20"/>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="22"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="28"/>
+      <c r="M2" s="29"/>
+    </row>
+    <row r="3" spans="1:13" ht="28.8">
+      <c r="A3" s="27"/>
       <c r="B3" s="2" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C3" s="2">
         <v>0.03</v>
@@ -693,577 +692,577 @@
       </c>
     </row>
     <row r="4" spans="1:13" ht="15.6">
-      <c r="A4" s="15">
+      <c r="A4" s="11">
         <v>0.1</v>
       </c>
-      <c r="B4" s="5">
-        <v>450</v>
+      <c r="B4" s="4">
+        <v>900</v>
       </c>
       <c r="C4" s="5">
-        <v>440</v>
+        <v>880</v>
       </c>
       <c r="D4" s="5">
-        <v>397</v>
+        <v>793</v>
       </c>
       <c r="E4" s="5">
-        <v>372</v>
+        <v>744</v>
       </c>
       <c r="F4" s="5">
-        <v>282</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="M4" s="9" t="s">
+        <v>564</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="I4" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="J4" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="K4" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="L4" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="M4" s="14" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="15.6">
-      <c r="A5" s="15">
+      <c r="A5" s="11">
         <v>0.15</v>
       </c>
-      <c r="B5" s="5">
-        <v>562</v>
+      <c r="B5" s="4">
+        <v>1130</v>
       </c>
       <c r="C5" s="5">
-        <v>562</v>
+        <v>1130</v>
       </c>
       <c r="D5" s="5">
-        <v>557</v>
+        <v>1120</v>
       </c>
       <c r="E5" s="5">
-        <v>549</v>
+        <v>1080</v>
       </c>
       <c r="F5" s="5">
-        <v>519</v>
+        <v>1037</v>
       </c>
       <c r="G5" s="5">
-        <v>462</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="M5" s="9" t="s">
+        <v>934</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="I5" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="J5" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="K5" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="L5" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="M5" s="14" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="15.6">
-      <c r="A6" s="15">
+      <c r="A6" s="11">
         <v>0.2</v>
       </c>
-      <c r="B6" s="5">
-        <v>675</v>
+      <c r="B6" s="4">
+        <v>1360</v>
       </c>
       <c r="C6" s="5">
-        <v>675</v>
+        <v>1360</v>
       </c>
       <c r="D6" s="5">
-        <v>675</v>
+        <v>1360</v>
       </c>
       <c r="E6" s="5">
-        <v>675</v>
+        <v>1360</v>
       </c>
       <c r="F6" s="5">
-        <v>669</v>
+        <v>1348</v>
       </c>
       <c r="G6" s="5">
-        <v>648</v>
+        <v>1314</v>
       </c>
       <c r="H6" s="5">
-        <v>539</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="K6" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="L6" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="M6" s="9" t="s">
+        <v>1085</v>
+      </c>
+      <c r="I6" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="J6" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="K6" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="L6" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="M6" s="14" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15.6">
-      <c r="A7" s="15">
+      <c r="A7" s="11">
         <v>0.25</v>
       </c>
-      <c r="B7" s="5">
-        <v>787</v>
+      <c r="B7" s="4">
+        <v>1582</v>
       </c>
       <c r="C7" s="5">
-        <v>787</v>
+        <v>1582</v>
       </c>
       <c r="D7" s="5">
-        <v>787</v>
+        <v>1582</v>
       </c>
       <c r="E7" s="5">
-        <v>787</v>
+        <v>1582</v>
       </c>
       <c r="F7" s="5">
-        <v>787</v>
+        <v>1582</v>
       </c>
       <c r="G7" s="5">
-        <v>785</v>
+        <v>1575</v>
       </c>
       <c r="H7" s="5">
-        <v>732</v>
+        <v>1458</v>
       </c>
       <c r="I7" s="5">
-        <v>568</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="K7" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="L7" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="M7" s="9" t="s">
+        <v>1109</v>
+      </c>
+      <c r="J7" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="K7" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="L7" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="M7" s="14" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="15.6">
-      <c r="A8" s="15">
+      <c r="A8" s="11">
         <v>0.3</v>
       </c>
-      <c r="B8" s="5">
-        <v>900</v>
+      <c r="B8" s="4">
+        <v>1816</v>
       </c>
       <c r="C8" s="5">
-        <v>900</v>
+        <v>1816</v>
       </c>
       <c r="D8" s="5">
-        <v>900</v>
+        <v>1816</v>
       </c>
       <c r="E8" s="5">
-        <v>900</v>
+        <v>1816</v>
       </c>
       <c r="F8" s="5">
-        <v>900</v>
+        <v>1816</v>
       </c>
       <c r="G8" s="5">
-        <v>900</v>
+        <v>1816</v>
       </c>
       <c r="H8" s="5">
-        <v>883</v>
+        <v>1789</v>
       </c>
       <c r="I8" s="5">
-        <v>803</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="K8" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="L8" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="M8" s="9" t="s">
+        <v>1617</v>
+      </c>
+      <c r="J8" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="K8" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="L8" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="M8" s="14" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="15.6">
-      <c r="A9" s="15">
+      <c r="A9" s="11">
         <v>0.4</v>
       </c>
-      <c r="B9" s="5">
-        <v>1125</v>
+      <c r="B9" s="4">
+        <v>2270</v>
       </c>
       <c r="C9" s="5">
-        <v>1125</v>
+        <v>2270</v>
       </c>
       <c r="D9" s="5">
-        <v>1125</v>
+        <v>2270</v>
       </c>
       <c r="E9" s="5">
-        <v>1125</v>
+        <v>2270</v>
       </c>
       <c r="F9" s="5">
-        <v>1125</v>
+        <v>2270</v>
       </c>
       <c r="G9" s="5">
-        <v>1125</v>
+        <v>2270</v>
       </c>
       <c r="H9" s="5">
-        <v>1125</v>
+        <v>2270</v>
       </c>
       <c r="I9" s="5">
-        <v>1115</v>
+        <v>2250</v>
       </c>
       <c r="J9" s="5">
-        <v>930</v>
-      </c>
-      <c r="K9" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="L9" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="M9" s="9" t="s">
+        <v>1878</v>
+      </c>
+      <c r="K9" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="L9" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="M9" s="14" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="15.6">
-      <c r="A10" s="15">
+      <c r="A10" s="11">
         <v>0.5</v>
       </c>
-      <c r="B10" s="5">
-        <v>1350</v>
+      <c r="B10" s="4">
+        <v>2724</v>
       </c>
       <c r="C10" s="5">
-        <v>1350</v>
+        <v>2724</v>
       </c>
       <c r="D10" s="5">
-        <v>1350</v>
+        <v>2724</v>
       </c>
       <c r="E10" s="5">
-        <v>1350</v>
+        <v>2724</v>
       </c>
       <c r="F10" s="5">
-        <v>1350</v>
+        <v>2724</v>
       </c>
       <c r="G10" s="5">
-        <v>1350</v>
+        <v>2724</v>
       </c>
       <c r="H10" s="5">
-        <v>1350</v>
+        <v>2724</v>
       </c>
       <c r="I10" s="5">
-        <v>1350</v>
+        <v>2724</v>
       </c>
       <c r="J10" s="5">
-        <v>1296</v>
+        <v>2632</v>
       </c>
       <c r="K10" s="5">
-        <v>1077</v>
-      </c>
-      <c r="L10" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="M10" s="9" t="s">
+        <v>2174</v>
+      </c>
+      <c r="L10" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="M10" s="14" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="15.6">
-      <c r="A11" s="15">
+      <c r="A11" s="11">
         <v>0.6</v>
       </c>
-      <c r="B11" s="5">
-        <v>1575</v>
+      <c r="B11" s="4">
+        <v>3178</v>
       </c>
       <c r="C11" s="5">
-        <v>1575</v>
+        <v>3178</v>
       </c>
       <c r="D11" s="5">
-        <v>1575</v>
+        <v>3178</v>
       </c>
       <c r="E11" s="5">
-        <v>1575</v>
+        <v>3178</v>
       </c>
       <c r="F11" s="5">
-        <v>1575</v>
+        <v>3178</v>
       </c>
       <c r="G11" s="5">
-        <v>1575</v>
+        <v>3178</v>
       </c>
       <c r="H11" s="5">
-        <v>1575</v>
+        <v>3178</v>
       </c>
       <c r="I11" s="5">
-        <v>1575</v>
+        <v>3178</v>
       </c>
       <c r="J11" s="5">
-        <v>1575</v>
+        <v>3178</v>
       </c>
       <c r="K11" s="5">
-        <v>1463</v>
+        <v>3164</v>
       </c>
       <c r="L11" s="5">
-        <v>1137</v>
-      </c>
-      <c r="M11" s="9" t="s">
+        <v>2294</v>
+      </c>
+      <c r="M11" s="14" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="15.6">
-      <c r="A12" s="15">
+      <c r="A12" s="11">
         <v>0.7</v>
       </c>
-      <c r="B12" s="5">
-        <v>1800</v>
+      <c r="B12" s="4">
+        <v>3632</v>
       </c>
       <c r="C12" s="5">
-        <v>1800</v>
+        <v>3632</v>
       </c>
       <c r="D12" s="5">
-        <v>1800</v>
+        <v>3632</v>
       </c>
       <c r="E12" s="5">
-        <v>1800</v>
+        <v>3632</v>
       </c>
       <c r="F12" s="5">
-        <v>1800</v>
+        <v>3632</v>
       </c>
       <c r="G12" s="5">
-        <v>1800</v>
+        <v>3632</v>
       </c>
       <c r="H12" s="5">
-        <v>1800</v>
+        <v>3632</v>
       </c>
       <c r="I12" s="5">
-        <v>1800</v>
+        <v>3632</v>
       </c>
       <c r="J12" s="5">
-        <v>1800</v>
+        <v>3632</v>
       </c>
       <c r="K12" s="5">
-        <v>1765</v>
+        <v>3599</v>
       </c>
       <c r="L12" s="5">
-        <v>1606</v>
+        <v>3287</v>
       </c>
       <c r="M12" s="9">
-        <v>1216</v>
+        <v>2492</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="15.6">
-      <c r="A13" s="15">
+      <c r="A13" s="11">
         <v>0.8</v>
       </c>
-      <c r="B13" s="5">
-        <v>2025</v>
+      <c r="B13" s="4">
+        <v>4086</v>
       </c>
       <c r="C13" s="5">
-        <v>2025</v>
+        <v>4086</v>
       </c>
       <c r="D13" s="5">
-        <v>2025</v>
+        <v>4086</v>
       </c>
       <c r="E13" s="5">
-        <v>2025</v>
+        <v>4086</v>
       </c>
       <c r="F13" s="5">
-        <v>2025</v>
+        <v>4086</v>
       </c>
       <c r="G13" s="5">
-        <v>2025</v>
+        <v>4086</v>
       </c>
       <c r="H13" s="5">
-        <v>2025</v>
+        <v>4086</v>
       </c>
       <c r="I13" s="5">
-        <v>2025</v>
+        <v>4086</v>
       </c>
       <c r="J13" s="5">
-        <v>2025</v>
+        <v>4086</v>
       </c>
       <c r="K13" s="5">
-        <v>2025</v>
+        <v>4086</v>
       </c>
       <c r="L13" s="5">
-        <v>1944</v>
+        <v>3948</v>
       </c>
       <c r="M13" s="9">
-        <v>1735</v>
+        <v>3501</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="15.6">
-      <c r="A14" s="15">
+      <c r="A14" s="11">
         <v>0.9</v>
       </c>
-      <c r="B14" s="5">
-        <v>2250</v>
+      <c r="B14" s="4">
+        <v>4541</v>
       </c>
       <c r="C14" s="5">
-        <v>2250</v>
+        <v>4541</v>
       </c>
       <c r="D14" s="5">
-        <v>2250</v>
+        <v>4541</v>
       </c>
       <c r="E14" s="5">
-        <v>2250</v>
+        <v>4541</v>
       </c>
       <c r="F14" s="5">
-        <v>2250</v>
+        <v>4541</v>
       </c>
       <c r="G14" s="5">
-        <v>2250</v>
+        <v>4541</v>
       </c>
       <c r="H14" s="5">
-        <v>2250</v>
+        <v>4541</v>
       </c>
       <c r="I14" s="5">
-        <v>2250</v>
+        <v>4541</v>
       </c>
       <c r="J14" s="5">
-        <v>2250</v>
+        <v>4541</v>
       </c>
       <c r="K14" s="5">
-        <v>2250</v>
+        <v>4541</v>
       </c>
       <c r="L14" s="5">
-        <v>2231</v>
+        <v>4502</v>
       </c>
       <c r="M14" s="9">
-        <v>2107</v>
+        <v>4254</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="15.6">
-      <c r="A15" s="15">
+      <c r="A15" s="11">
         <v>1</v>
       </c>
-      <c r="B15" s="5">
-        <v>2475</v>
+      <c r="B15" s="4">
+        <v>4995</v>
       </c>
       <c r="C15" s="5">
-        <v>2475</v>
+        <v>4995</v>
       </c>
       <c r="D15" s="5">
-        <v>2475</v>
+        <v>4995</v>
       </c>
       <c r="E15" s="5">
-        <v>2475</v>
+        <v>4995</v>
       </c>
       <c r="F15" s="5">
-        <v>2475</v>
+        <v>4995</v>
       </c>
       <c r="G15" s="5">
-        <v>2475</v>
+        <v>4995</v>
       </c>
       <c r="H15" s="5">
-        <v>2475</v>
+        <v>4995</v>
       </c>
       <c r="I15" s="5">
-        <v>2475</v>
+        <v>4995</v>
       </c>
       <c r="J15" s="5">
-        <v>2475</v>
+        <v>4995</v>
       </c>
       <c r="K15" s="5">
-        <v>2475</v>
+        <v>4995</v>
       </c>
       <c r="L15" s="5">
-        <v>2472</v>
+        <v>4954</v>
       </c>
       <c r="M15" s="9">
-        <v>2417</v>
+        <v>4879</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="15.6">
-      <c r="A16" s="15">
+      <c r="A16" s="11">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B16" s="12">
-        <v>2700</v>
+      <c r="B16" s="4">
+        <v>5736</v>
       </c>
       <c r="C16" s="5">
-        <v>2700</v>
+        <v>5736</v>
       </c>
       <c r="D16" s="5">
-        <v>2700</v>
+        <v>5736</v>
       </c>
       <c r="E16" s="5">
-        <v>2700</v>
+        <v>5736</v>
       </c>
       <c r="F16" s="5">
-        <v>2700</v>
+        <v>5736</v>
       </c>
       <c r="G16" s="5">
-        <v>2700</v>
+        <v>5736</v>
       </c>
       <c r="H16" s="5">
-        <v>2700</v>
+        <v>5736</v>
       </c>
       <c r="I16" s="5">
-        <v>2700</v>
+        <v>5736</v>
       </c>
       <c r="J16" s="5">
-        <v>2700</v>
+        <v>5736</v>
       </c>
       <c r="K16" s="5">
-        <v>2700</v>
+        <v>5736</v>
       </c>
       <c r="L16" s="5">
-        <v>2700</v>
+        <v>5732</v>
       </c>
       <c r="M16" s="9">
-        <v>2688</v>
+        <v>5711</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="15.6">
-      <c r="A17" s="16">
+      <c r="A17" s="13">
         <v>1.2</v>
       </c>
-      <c r="B17" s="17">
-        <v>2925</v>
+      <c r="B17" s="6">
+        <v>6500</v>
       </c>
       <c r="C17" s="7">
-        <v>2925</v>
+        <v>6500</v>
       </c>
       <c r="D17" s="7">
-        <v>2925</v>
+        <v>6500</v>
       </c>
       <c r="E17" s="7">
-        <v>2925</v>
+        <v>6500</v>
       </c>
       <c r="F17" s="7">
-        <v>2925</v>
+        <v>6500</v>
       </c>
       <c r="G17" s="7">
-        <v>2925</v>
+        <v>6500</v>
       </c>
       <c r="H17" s="7">
-        <v>2925</v>
+        <v>6500</v>
       </c>
       <c r="I17" s="7">
-        <v>2925</v>
+        <v>6500</v>
       </c>
       <c r="J17" s="7">
-        <v>2925</v>
+        <v>6500</v>
       </c>
       <c r="K17" s="7">
-        <v>2925</v>
+        <v>6500</v>
       </c>
       <c r="L17" s="7">
-        <v>2925</v>
+        <v>6500</v>
       </c>
       <c r="M17" s="10">
-        <v>2925</v>
+        <v>6500</v>
       </c>
     </row>
   </sheetData>
@@ -1280,15 +1279,16 @@
   <dimension ref="A1:M17"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="9.109375" customWidth="1"/>
+    <col min="1" max="1" width="33.5546875" customWidth="1"/>
+    <col min="2" max="2" width="38.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="22.95" customHeight="1">
+    <row r="1" spans="1:13" ht="21" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -1302,29 +1302,29 @@
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
     </row>
-    <row r="2" spans="1:13" ht="19.5" customHeight="1">
-      <c r="A2" s="21" t="s">
+    <row r="2" spans="1:13" ht="18.75" customHeight="1">
+      <c r="A2" s="26" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23"/>
-      <c r="H2" s="23"/>
-      <c r="I2" s="23"/>
-      <c r="J2" s="23"/>
-      <c r="K2" s="23"/>
-      <c r="L2" s="23"/>
-      <c r="M2" s="24"/>
-    </row>
-    <row r="3" spans="1:13" ht="28.8">
-      <c r="A3" s="22"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="24"/>
+      <c r="L2" s="24"/>
+      <c r="M2" s="25"/>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="27"/>
       <c r="B3" s="2" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C3" s="2">
         <v>0.03</v>
@@ -1361,577 +1361,577 @@
       </c>
     </row>
     <row r="4" spans="1:13" ht="15.6">
-      <c r="A4" s="11">
+      <c r="A4" s="15">
         <v>0.1</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="5">
+        <v>450</v>
+      </c>
+      <c r="C4" s="5">
+        <v>440</v>
+      </c>
+      <c r="D4" s="5">
+        <v>397</v>
+      </c>
+      <c r="E4" s="5">
+        <v>372</v>
+      </c>
+      <c r="F4" s="5">
+        <v>282</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="M4" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="15.6">
+      <c r="A5" s="15">
+        <v>0.15</v>
+      </c>
+      <c r="B5" s="5">
+        <v>562</v>
+      </c>
+      <c r="C5" s="5">
+        <v>562</v>
+      </c>
+      <c r="D5" s="5">
+        <v>557</v>
+      </c>
+      <c r="E5" s="5">
+        <v>549</v>
+      </c>
+      <c r="F5" s="5">
+        <v>519</v>
+      </c>
+      <c r="G5" s="5">
+        <v>462</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="M5" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="15.6">
+      <c r="A6" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="B6" s="5">
+        <v>675</v>
+      </c>
+      <c r="C6" s="5">
+        <v>675</v>
+      </c>
+      <c r="D6" s="5">
+        <v>675</v>
+      </c>
+      <c r="E6" s="5">
+        <v>675</v>
+      </c>
+      <c r="F6" s="5">
+        <v>669</v>
+      </c>
+      <c r="G6" s="5">
+        <v>648</v>
+      </c>
+      <c r="H6" s="5">
+        <v>539</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="M6" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="15.6">
+      <c r="A7" s="15">
+        <v>0.25</v>
+      </c>
+      <c r="B7" s="5">
+        <v>787</v>
+      </c>
+      <c r="C7" s="5">
+        <v>787</v>
+      </c>
+      <c r="D7" s="5">
+        <v>787</v>
+      </c>
+      <c r="E7" s="5">
+        <v>787</v>
+      </c>
+      <c r="F7" s="5">
+        <v>787</v>
+      </c>
+      <c r="G7" s="5">
+        <v>785</v>
+      </c>
+      <c r="H7" s="5">
+        <v>732</v>
+      </c>
+      <c r="I7" s="5">
+        <v>568</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="M7" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="15.6">
+      <c r="A8" s="15">
+        <v>0.3</v>
+      </c>
+      <c r="B8" s="5">
         <v>900</v>
       </c>
-      <c r="C4" s="5">
-        <v>880</v>
-      </c>
-      <c r="D4" s="5">
-        <v>793</v>
-      </c>
-      <c r="E4" s="5">
-        <v>744</v>
-      </c>
-      <c r="F4" s="5">
-        <v>564</v>
-      </c>
-      <c r="G4" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="H4" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="I4" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="J4" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="K4" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="L4" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="M4" s="14" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="15.6">
-      <c r="A5" s="11">
-        <v>0.15</v>
-      </c>
-      <c r="B5" s="4">
-        <v>1130</v>
-      </c>
-      <c r="C5" s="5">
-        <v>1130</v>
-      </c>
-      <c r="D5" s="5">
-        <v>1120</v>
-      </c>
-      <c r="E5" s="5">
-        <v>1080</v>
-      </c>
-      <c r="F5" s="5">
-        <v>1037</v>
-      </c>
-      <c r="G5" s="5">
-        <v>934</v>
-      </c>
-      <c r="H5" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="I5" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="J5" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="K5" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="L5" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="M5" s="14" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="15.6">
-      <c r="A6" s="11">
-        <v>0.2</v>
-      </c>
-      <c r="B6" s="4">
-        <v>1360</v>
-      </c>
-      <c r="C6" s="5">
-        <v>1360</v>
-      </c>
-      <c r="D6" s="5">
-        <v>1360</v>
-      </c>
-      <c r="E6" s="5">
-        <v>1360</v>
-      </c>
-      <c r="F6" s="5">
-        <v>1348</v>
-      </c>
-      <c r="G6" s="5">
-        <v>1314</v>
-      </c>
-      <c r="H6" s="5">
-        <v>1085</v>
-      </c>
-      <c r="I6" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="J6" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="K6" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="L6" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="M6" s="14" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="15.6">
-      <c r="A7" s="11">
-        <v>0.25</v>
-      </c>
-      <c r="B7" s="4">
-        <v>1582</v>
-      </c>
-      <c r="C7" s="5">
-        <v>1582</v>
-      </c>
-      <c r="D7" s="5">
-        <v>1582</v>
-      </c>
-      <c r="E7" s="5">
-        <v>1582</v>
-      </c>
-      <c r="F7" s="5">
-        <v>1582</v>
-      </c>
-      <c r="G7" s="5">
+      <c r="C8" s="5">
+        <v>900</v>
+      </c>
+      <c r="D8" s="5">
+        <v>900</v>
+      </c>
+      <c r="E8" s="5">
+        <v>900</v>
+      </c>
+      <c r="F8" s="5">
+        <v>900</v>
+      </c>
+      <c r="G8" s="5">
+        <v>900</v>
+      </c>
+      <c r="H8" s="5">
+        <v>883</v>
+      </c>
+      <c r="I8" s="5">
+        <v>803</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="M8" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="15.6">
+      <c r="A9" s="15">
+        <v>0.4</v>
+      </c>
+      <c r="B9" s="5">
+        <v>1125</v>
+      </c>
+      <c r="C9" s="5">
+        <v>1125</v>
+      </c>
+      <c r="D9" s="5">
+        <v>1125</v>
+      </c>
+      <c r="E9" s="5">
+        <v>1125</v>
+      </c>
+      <c r="F9" s="5">
+        <v>1125</v>
+      </c>
+      <c r="G9" s="5">
+        <v>1125</v>
+      </c>
+      <c r="H9" s="5">
+        <v>1125</v>
+      </c>
+      <c r="I9" s="5">
+        <v>1115</v>
+      </c>
+      <c r="J9" s="5">
+        <v>930</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="M9" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="15.6">
+      <c r="A10" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="B10" s="5">
+        <v>1350</v>
+      </c>
+      <c r="C10" s="5">
+        <v>1350</v>
+      </c>
+      <c r="D10" s="5">
+        <v>1350</v>
+      </c>
+      <c r="E10" s="5">
+        <v>1350</v>
+      </c>
+      <c r="F10" s="5">
+        <v>1350</v>
+      </c>
+      <c r="G10" s="5">
+        <v>1350</v>
+      </c>
+      <c r="H10" s="5">
+        <v>1350</v>
+      </c>
+      <c r="I10" s="5">
+        <v>1350</v>
+      </c>
+      <c r="J10" s="5">
+        <v>1296</v>
+      </c>
+      <c r="K10" s="5">
+        <v>1077</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="M10" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="15.6">
+      <c r="A11" s="15">
+        <v>0.6</v>
+      </c>
+      <c r="B11" s="5">
         <v>1575</v>
       </c>
-      <c r="H7" s="5">
-        <v>1458</v>
-      </c>
-      <c r="I7" s="5">
-        <v>1109</v>
-      </c>
-      <c r="J7" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="K7" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="L7" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="M7" s="14" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="15.6">
-      <c r="A8" s="11">
-        <v>0.3</v>
-      </c>
-      <c r="B8" s="4">
-        <v>1816</v>
-      </c>
-      <c r="C8" s="5">
-        <v>1816</v>
-      </c>
-      <c r="D8" s="5">
-        <v>1816</v>
-      </c>
-      <c r="E8" s="5">
-        <v>1816</v>
-      </c>
-      <c r="F8" s="5">
-        <v>1816</v>
-      </c>
-      <c r="G8" s="5">
-        <v>1816</v>
-      </c>
-      <c r="H8" s="5">
-        <v>1789</v>
-      </c>
-      <c r="I8" s="5">
-        <v>1617</v>
-      </c>
-      <c r="J8" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="K8" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="L8" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="M8" s="14" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="15.6">
-      <c r="A9" s="11">
-        <v>0.4</v>
-      </c>
-      <c r="B9" s="4">
-        <v>2270</v>
-      </c>
-      <c r="C9" s="5">
-        <v>2270</v>
-      </c>
-      <c r="D9" s="5">
-        <v>2270</v>
-      </c>
-      <c r="E9" s="5">
-        <v>2270</v>
-      </c>
-      <c r="F9" s="5">
-        <v>2270</v>
-      </c>
-      <c r="G9" s="5">
-        <v>2270</v>
-      </c>
-      <c r="H9" s="5">
-        <v>2270</v>
-      </c>
-      <c r="I9" s="5">
+      <c r="C11" s="5">
+        <v>1575</v>
+      </c>
+      <c r="D11" s="5">
+        <v>1575</v>
+      </c>
+      <c r="E11" s="5">
+        <v>1575</v>
+      </c>
+      <c r="F11" s="5">
+        <v>1575</v>
+      </c>
+      <c r="G11" s="5">
+        <v>1575</v>
+      </c>
+      <c r="H11" s="5">
+        <v>1575</v>
+      </c>
+      <c r="I11" s="5">
+        <v>1575</v>
+      </c>
+      <c r="J11" s="5">
+        <v>1575</v>
+      </c>
+      <c r="K11" s="5">
+        <v>1463</v>
+      </c>
+      <c r="L11" s="5">
+        <v>1137</v>
+      </c>
+      <c r="M11" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="15.6">
+      <c r="A12" s="15">
+        <v>0.7</v>
+      </c>
+      <c r="B12" s="5">
+        <v>1800</v>
+      </c>
+      <c r="C12" s="5">
+        <v>1800</v>
+      </c>
+      <c r="D12" s="5">
+        <v>1800</v>
+      </c>
+      <c r="E12" s="5">
+        <v>1800</v>
+      </c>
+      <c r="F12" s="5">
+        <v>1800</v>
+      </c>
+      <c r="G12" s="5">
+        <v>1800</v>
+      </c>
+      <c r="H12" s="5">
+        <v>1800</v>
+      </c>
+      <c r="I12" s="5">
+        <v>1800</v>
+      </c>
+      <c r="J12" s="5">
+        <v>1800</v>
+      </c>
+      <c r="K12" s="5">
+        <v>1765</v>
+      </c>
+      <c r="L12" s="5">
+        <v>1606</v>
+      </c>
+      <c r="M12" s="9">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="15.6">
+      <c r="A13" s="15">
+        <v>0.8</v>
+      </c>
+      <c r="B13" s="5">
+        <v>2025</v>
+      </c>
+      <c r="C13" s="5">
+        <v>2025</v>
+      </c>
+      <c r="D13" s="5">
+        <v>2025</v>
+      </c>
+      <c r="E13" s="5">
+        <v>2025</v>
+      </c>
+      <c r="F13" s="5">
+        <v>2025</v>
+      </c>
+      <c r="G13" s="5">
+        <v>2025</v>
+      </c>
+      <c r="H13" s="5">
+        <v>2025</v>
+      </c>
+      <c r="I13" s="5">
+        <v>2025</v>
+      </c>
+      <c r="J13" s="5">
+        <v>2025</v>
+      </c>
+      <c r="K13" s="5">
+        <v>2025</v>
+      </c>
+      <c r="L13" s="5">
+        <v>1944</v>
+      </c>
+      <c r="M13" s="9">
+        <v>1735</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="15.6">
+      <c r="A14" s="15">
+        <v>0.9</v>
+      </c>
+      <c r="B14" s="5">
         <v>2250</v>
       </c>
-      <c r="J9" s="5">
-        <v>1878</v>
-      </c>
-      <c r="K9" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="L9" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="M9" s="14" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="15.6">
-      <c r="A10" s="11">
-        <v>0.5</v>
-      </c>
-      <c r="B10" s="4">
-        <v>2724</v>
-      </c>
-      <c r="C10" s="5">
-        <v>2724</v>
-      </c>
-      <c r="D10" s="5">
-        <v>2724</v>
-      </c>
-      <c r="E10" s="5">
-        <v>2724</v>
-      </c>
-      <c r="F10" s="5">
-        <v>2724</v>
-      </c>
-      <c r="G10" s="5">
-        <v>2724</v>
-      </c>
-      <c r="H10" s="5">
-        <v>2724</v>
-      </c>
-      <c r="I10" s="5">
-        <v>2724</v>
-      </c>
-      <c r="J10" s="5">
-        <v>2632</v>
-      </c>
-      <c r="K10" s="5">
-        <v>2174</v>
-      </c>
-      <c r="L10" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="M10" s="14" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="15.6">
-      <c r="A11" s="11">
-        <v>0.6</v>
-      </c>
-      <c r="B11" s="4">
-        <v>3178</v>
-      </c>
-      <c r="C11" s="5">
-        <v>3178</v>
-      </c>
-      <c r="D11" s="5">
-        <v>3178</v>
-      </c>
-      <c r="E11" s="5">
-        <v>3178</v>
-      </c>
-      <c r="F11" s="5">
-        <v>3178</v>
-      </c>
-      <c r="G11" s="5">
-        <v>3178</v>
-      </c>
-      <c r="H11" s="5">
-        <v>3178</v>
-      </c>
-      <c r="I11" s="5">
-        <v>3178</v>
-      </c>
-      <c r="J11" s="5">
-        <v>3178</v>
-      </c>
-      <c r="K11" s="5">
-        <v>3164</v>
-      </c>
-      <c r="L11" s="5">
-        <v>2294</v>
-      </c>
-      <c r="M11" s="14" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="15.6">
-      <c r="A12" s="11">
-        <v>0.7</v>
-      </c>
-      <c r="B12" s="4">
-        <v>3632</v>
-      </c>
-      <c r="C12" s="5">
-        <v>3632</v>
-      </c>
-      <c r="D12" s="5">
-        <v>3632</v>
-      </c>
-      <c r="E12" s="5">
-        <v>3632</v>
-      </c>
-      <c r="F12" s="5">
-        <v>3632</v>
-      </c>
-      <c r="G12" s="5">
-        <v>3632</v>
-      </c>
-      <c r="H12" s="5">
-        <v>3632</v>
-      </c>
-      <c r="I12" s="5">
-        <v>3632</v>
-      </c>
-      <c r="J12" s="5">
-        <v>3632</v>
-      </c>
-      <c r="K12" s="5">
-        <v>3599</v>
-      </c>
-      <c r="L12" s="5">
-        <v>3287</v>
-      </c>
-      <c r="M12" s="9">
-        <v>2492</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="15.6">
-      <c r="A13" s="11">
-        <v>0.8</v>
-      </c>
-      <c r="B13" s="4">
-        <v>4086</v>
-      </c>
-      <c r="C13" s="5">
-        <v>4086</v>
-      </c>
-      <c r="D13" s="5">
-        <v>4086</v>
-      </c>
-      <c r="E13" s="5">
-        <v>4086</v>
-      </c>
-      <c r="F13" s="5">
-        <v>4086</v>
-      </c>
-      <c r="G13" s="5">
-        <v>4086</v>
-      </c>
-      <c r="H13" s="5">
-        <v>4086</v>
-      </c>
-      <c r="I13" s="5">
-        <v>4086</v>
-      </c>
-      <c r="J13" s="5">
-        <v>4086</v>
-      </c>
-      <c r="K13" s="5">
-        <v>4086</v>
-      </c>
-      <c r="L13" s="5">
-        <v>3948</v>
-      </c>
-      <c r="M13" s="9">
-        <v>3501</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="15.6">
-      <c r="A14" s="11">
-        <v>0.9</v>
-      </c>
-      <c r="B14" s="4">
-        <v>4541</v>
-      </c>
       <c r="C14" s="5">
-        <v>4541</v>
+        <v>2250</v>
       </c>
       <c r="D14" s="5">
-        <v>4541</v>
+        <v>2250</v>
       </c>
       <c r="E14" s="5">
-        <v>4541</v>
+        <v>2250</v>
       </c>
       <c r="F14" s="5">
-        <v>4541</v>
+        <v>2250</v>
       </c>
       <c r="G14" s="5">
-        <v>4541</v>
+        <v>2250</v>
       </c>
       <c r="H14" s="5">
-        <v>4541</v>
+        <v>2250</v>
       </c>
       <c r="I14" s="5">
-        <v>4541</v>
+        <v>2250</v>
       </c>
       <c r="J14" s="5">
-        <v>4541</v>
+        <v>2250</v>
       </c>
       <c r="K14" s="5">
-        <v>4541</v>
+        <v>2250</v>
       </c>
       <c r="L14" s="5">
-        <v>4502</v>
+        <v>2231</v>
       </c>
       <c r="M14" s="9">
-        <v>4254</v>
+        <v>2107</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="15.6">
-      <c r="A15" s="11">
+      <c r="A15" s="15">
         <v>1</v>
       </c>
-      <c r="B15" s="4">
-        <v>4995</v>
+      <c r="B15" s="5">
+        <v>2475</v>
       </c>
       <c r="C15" s="5">
-        <v>4995</v>
+        <v>2475</v>
       </c>
       <c r="D15" s="5">
-        <v>4995</v>
+        <v>2475</v>
       </c>
       <c r="E15" s="5">
-        <v>4995</v>
+        <v>2475</v>
       </c>
       <c r="F15" s="5">
-        <v>4995</v>
+        <v>2475</v>
       </c>
       <c r="G15" s="5">
-        <v>4995</v>
+        <v>2475</v>
       </c>
       <c r="H15" s="5">
-        <v>4995</v>
+        <v>2475</v>
       </c>
       <c r="I15" s="5">
-        <v>4995</v>
+        <v>2475</v>
       </c>
       <c r="J15" s="5">
-        <v>4995</v>
+        <v>2475</v>
       </c>
       <c r="K15" s="5">
-        <v>4995</v>
+        <v>2475</v>
       </c>
       <c r="L15" s="5">
-        <v>4954</v>
+        <v>2472</v>
       </c>
       <c r="M15" s="9">
-        <v>4879</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="15.6">
-      <c r="A16" s="11">
+      <c r="A16" s="15">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B16" s="4">
-        <v>5736</v>
+      <c r="B16" s="12">
+        <v>2700</v>
       </c>
       <c r="C16" s="5">
-        <v>5736</v>
+        <v>2700</v>
       </c>
       <c r="D16" s="5">
-        <v>5736</v>
+        <v>2700</v>
       </c>
       <c r="E16" s="5">
-        <v>5736</v>
+        <v>2700</v>
       </c>
       <c r="F16" s="5">
-        <v>5736</v>
+        <v>2700</v>
       </c>
       <c r="G16" s="5">
-        <v>5736</v>
+        <v>2700</v>
       </c>
       <c r="H16" s="5">
-        <v>5736</v>
+        <v>2700</v>
       </c>
       <c r="I16" s="5">
-        <v>5736</v>
+        <v>2700</v>
       </c>
       <c r="J16" s="5">
-        <v>5736</v>
+        <v>2700</v>
       </c>
       <c r="K16" s="5">
-        <v>5736</v>
+        <v>2700</v>
       </c>
       <c r="L16" s="5">
-        <v>5732</v>
+        <v>2700</v>
       </c>
       <c r="M16" s="9">
-        <v>5711</v>
+        <v>2688</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="15.6">
-      <c r="A17" s="13">
+      <c r="A17" s="16">
         <v>1.2</v>
       </c>
-      <c r="B17" s="6">
-        <v>6500</v>
+      <c r="B17" s="17">
+        <v>2925</v>
       </c>
       <c r="C17" s="7">
-        <v>6500</v>
+        <v>2925</v>
       </c>
       <c r="D17" s="7">
-        <v>6500</v>
+        <v>2925</v>
       </c>
       <c r="E17" s="7">
-        <v>6500</v>
+        <v>2925</v>
       </c>
       <c r="F17" s="7">
-        <v>6500</v>
+        <v>2925</v>
       </c>
       <c r="G17" s="7">
-        <v>6500</v>
+        <v>2925</v>
       </c>
       <c r="H17" s="7">
-        <v>6500</v>
+        <v>2925</v>
       </c>
       <c r="I17" s="7">
-        <v>6500</v>
+        <v>2925</v>
       </c>
       <c r="J17" s="7">
-        <v>6500</v>
+        <v>2925</v>
       </c>
       <c r="K17" s="7">
-        <v>6500</v>
+        <v>2925</v>
       </c>
       <c r="L17" s="7">
-        <v>6500</v>
+        <v>2925</v>
       </c>
       <c r="M17" s="10">
-        <v>6500</v>
+        <v>2925</v>
       </c>
     </row>
   </sheetData>
@@ -1972,26 +1972,26 @@
       <c r="M1" s="1"/>
     </row>
     <row r="2" spans="1:13" ht="19.5" customHeight="1">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="26"/>
-      <c r="M2" s="27"/>
-    </row>
-    <row r="3" spans="1:13" ht="28.8">
-      <c r="A3" s="29"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
+      <c r="L2" s="19"/>
+      <c r="M2" s="20"/>
+    </row>
+    <row r="3" spans="1:13" ht="15.6">
+      <c r="A3" s="22"/>
       <c r="B3" s="2" t="s">
         <v>7</v>
       </c>

--- a/Регулятор давления РДГ-50Н(В).xlsx
+++ b/Регулятор давления РДГ-50Н(В).xlsx
@@ -4,19 +4,21 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28620" windowHeight="13020"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28620" windowHeight="13020" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="РДГ-50Н(В) седло 35 мм" sheetId="4" r:id="rId1"/>
     <sheet name="РДГ-50Н(В) седло 25 мм" sheetId="3" r:id="rId2"/>
     <sheet name="РДГ-50Н(В) седло 42 мм" sheetId="5" r:id="rId3"/>
+    <sheet name="РДГ-50Н(В)Ж" sheetId="6" r:id="rId4"/>
+    <sheet name="Лист1" sheetId="7" r:id="rId5"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="19">
   <si>
     <t>РДГ-50Н(В)</t>
   </si>
@@ -44,12 +46,45 @@
   <si>
     <t>седло 42 мм</t>
   </si>
+  <si>
+    <t>РДГ-50Н(В)Ж</t>
+  </si>
+  <si>
+    <t>Седло 3 мм</t>
+  </si>
+  <si>
+    <t>РДГД-20М1-1,2</t>
+  </si>
+  <si>
+    <t>РДГД-20М-1,2</t>
+  </si>
+  <si>
+    <t>РДГД-20М2-1,2</t>
+  </si>
+  <si>
+    <t>РДГД-20М3-1,2</t>
+  </si>
+  <si>
+    <t>0,001-0,002</t>
+  </si>
+  <si>
+    <t>0,002-0,0025</t>
+  </si>
+  <si>
+    <t>0,0025-0,0035</t>
+  </si>
+  <si>
+    <t>0,0035-0,005</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="6">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -89,8 +124,29 @@
       <name val="Ubuntu"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -103,8 +159,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
+        <bgColor rgb="FFC0C0C0"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="12">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -239,13 +301,65 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color auto="1"/>
+      </left>
+      <right style="hair">
+        <color auto="1"/>
+      </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -315,6 +429,18 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -324,17 +450,26 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="2" fontId="6" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -634,26 +769,26 @@
       <c r="M1" s="1"/>
     </row>
     <row r="2" spans="1:13" ht="19.5" customHeight="1">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="28"/>
-      <c r="J2" s="28"/>
-      <c r="K2" s="28"/>
-      <c r="L2" s="28"/>
-      <c r="M2" s="29"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="23"/>
+      <c r="M2" s="24"/>
     </row>
     <row r="3" spans="1:13" ht="28.8">
-      <c r="A3" s="27"/>
+      <c r="A3" s="26"/>
       <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
@@ -1303,26 +1438,26 @@
       <c r="M1" s="1"/>
     </row>
     <row r="2" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="24"/>
-      <c r="L2" s="24"/>
-      <c r="M2" s="25"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="28"/>
+      <c r="M2" s="29"/>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="27"/>
+      <c r="A3" s="26"/>
       <c r="B3" s="2" t="s">
         <v>4</v>
       </c>
@@ -2606,4 +2741,954 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555596" footer="0.51180555555555596"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:M17"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="40.88671875" customWidth="1"/>
+    <col min="2" max="2" width="32.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="22.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+    </row>
+    <row r="2" spans="1:13" ht="19.5" customHeight="1">
+      <c r="A2" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
+      <c r="L2" s="19"/>
+      <c r="M2" s="20"/>
+    </row>
+    <row r="3" spans="1:13" ht="15.6">
+      <c r="A3" s="22"/>
+      <c r="B3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0.06</v>
+      </c>
+      <c r="F3" s="2">
+        <v>0.08</v>
+      </c>
+      <c r="G3" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="H3" s="2">
+        <v>0.15</v>
+      </c>
+      <c r="I3" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="J3" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="K3" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="L3" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="M3" s="8">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="15" customHeight="1">
+      <c r="A4" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="B4" s="4">
+        <v>1200</v>
+      </c>
+      <c r="C4" s="5">
+        <v>1160</v>
+      </c>
+      <c r="D4" s="5">
+        <v>1070</v>
+      </c>
+      <c r="E4" s="5">
+        <v>992</v>
+      </c>
+      <c r="F4" s="5">
+        <v>753</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="M4" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="15" customHeight="1">
+      <c r="A5" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="B5" s="4">
+        <v>1500</v>
+      </c>
+      <c r="C5" s="5">
+        <v>1500</v>
+      </c>
+      <c r="D5" s="5">
+        <v>1487</v>
+      </c>
+      <c r="E5" s="5">
+        <v>1460</v>
+      </c>
+      <c r="F5" s="5">
+        <v>1380</v>
+      </c>
+      <c r="G5" s="5">
+        <v>1241</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="M5" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="15" customHeight="1">
+      <c r="A6" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="B6" s="4">
+        <v>1800</v>
+      </c>
+      <c r="C6" s="5">
+        <v>1800</v>
+      </c>
+      <c r="D6" s="5">
+        <v>1800</v>
+      </c>
+      <c r="E6" s="5">
+        <v>1800</v>
+      </c>
+      <c r="F6" s="5">
+        <v>1785</v>
+      </c>
+      <c r="G6" s="5">
+        <v>1728</v>
+      </c>
+      <c r="H6" s="5">
+        <v>1436</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="M6" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="15" customHeight="1">
+      <c r="A7" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="B7" s="4">
+        <v>2102</v>
+      </c>
+      <c r="C7" s="5">
+        <v>2102</v>
+      </c>
+      <c r="D7" s="5">
+        <v>2102</v>
+      </c>
+      <c r="E7" s="5">
+        <v>2102</v>
+      </c>
+      <c r="F7" s="5">
+        <v>2102</v>
+      </c>
+      <c r="G7" s="5">
+        <v>2095</v>
+      </c>
+      <c r="H7" s="5">
+        <v>1953</v>
+      </c>
+      <c r="I7" s="5">
+        <v>1517</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="M7" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="15" customHeight="1">
+      <c r="A8" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="B8" s="4">
+        <v>2400</v>
+      </c>
+      <c r="C8" s="5">
+        <v>2400</v>
+      </c>
+      <c r="D8" s="5">
+        <v>2400</v>
+      </c>
+      <c r="E8" s="5">
+        <v>2400</v>
+      </c>
+      <c r="F8" s="5">
+        <v>2400</v>
+      </c>
+      <c r="G8" s="5">
+        <v>2400</v>
+      </c>
+      <c r="H8" s="5">
+        <v>2355</v>
+      </c>
+      <c r="I8" s="5">
+        <v>2143</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="M8" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="15" customHeight="1">
+      <c r="A9" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="B9" s="4">
+        <v>3000</v>
+      </c>
+      <c r="C9" s="5">
+        <v>3000</v>
+      </c>
+      <c r="D9" s="5">
+        <v>3000</v>
+      </c>
+      <c r="E9" s="5">
+        <v>3000</v>
+      </c>
+      <c r="F9" s="5">
+        <v>3000</v>
+      </c>
+      <c r="G9" s="5">
+        <v>3000</v>
+      </c>
+      <c r="H9" s="5">
+        <v>3000</v>
+      </c>
+      <c r="I9" s="5">
+        <v>2975</v>
+      </c>
+      <c r="J9" s="5">
+        <v>2483</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="M9" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="15" customHeight="1">
+      <c r="A10" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="B10" s="4">
+        <v>3600</v>
+      </c>
+      <c r="C10" s="5">
+        <v>3600</v>
+      </c>
+      <c r="D10" s="5">
+        <v>3600</v>
+      </c>
+      <c r="E10" s="5">
+        <v>3600</v>
+      </c>
+      <c r="F10" s="5">
+        <v>3600</v>
+      </c>
+      <c r="G10" s="5">
+        <v>3600</v>
+      </c>
+      <c r="H10" s="5">
+        <v>3600</v>
+      </c>
+      <c r="I10" s="5">
+        <v>3600</v>
+      </c>
+      <c r="J10" s="5">
+        <v>3460</v>
+      </c>
+      <c r="K10" s="5">
+        <v>2875</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="M10" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="15" customHeight="1">
+      <c r="A11" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="B11" s="4">
+        <v>4200</v>
+      </c>
+      <c r="C11" s="5">
+        <v>4200</v>
+      </c>
+      <c r="D11" s="5">
+        <v>4200</v>
+      </c>
+      <c r="E11" s="5">
+        <v>4200</v>
+      </c>
+      <c r="F11" s="5">
+        <v>4200</v>
+      </c>
+      <c r="G11" s="5">
+        <v>4200</v>
+      </c>
+      <c r="H11" s="5">
+        <v>4200</v>
+      </c>
+      <c r="I11" s="5">
+        <v>4200</v>
+      </c>
+      <c r="J11" s="5">
+        <v>4190</v>
+      </c>
+      <c r="K11" s="5">
+        <v>3906</v>
+      </c>
+      <c r="L11" s="5">
+        <v>3035</v>
+      </c>
+      <c r="M11" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="15" customHeight="1">
+      <c r="A12" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="B12" s="4">
+        <v>4800</v>
+      </c>
+      <c r="C12" s="5">
+        <v>4800</v>
+      </c>
+      <c r="D12" s="5">
+        <v>4800</v>
+      </c>
+      <c r="E12" s="5">
+        <v>4800</v>
+      </c>
+      <c r="F12" s="5">
+        <v>4800</v>
+      </c>
+      <c r="G12" s="5">
+        <v>4800</v>
+      </c>
+      <c r="H12" s="5">
+        <v>4800</v>
+      </c>
+      <c r="I12" s="5">
+        <v>4800</v>
+      </c>
+      <c r="J12" s="5">
+        <v>4800</v>
+      </c>
+      <c r="K12" s="5">
+        <v>4713</v>
+      </c>
+      <c r="L12" s="5">
+        <v>4288</v>
+      </c>
+      <c r="M12" s="9">
+        <v>3246</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="15" customHeight="1">
+      <c r="A13" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="B13" s="4">
+        <v>5400</v>
+      </c>
+      <c r="C13" s="5">
+        <v>5400</v>
+      </c>
+      <c r="D13" s="5">
+        <v>5400</v>
+      </c>
+      <c r="E13" s="5">
+        <v>5400</v>
+      </c>
+      <c r="F13" s="5">
+        <v>5400</v>
+      </c>
+      <c r="G13" s="5">
+        <v>5400</v>
+      </c>
+      <c r="H13" s="5">
+        <v>5400</v>
+      </c>
+      <c r="I13" s="5">
+        <v>5400</v>
+      </c>
+      <c r="J13" s="5">
+        <v>5400</v>
+      </c>
+      <c r="K13" s="5">
+        <v>5390</v>
+      </c>
+      <c r="L13" s="5">
+        <v>5188</v>
+      </c>
+      <c r="M13" s="9">
+        <v>4630</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="15" customHeight="1">
+      <c r="A14" s="3">
+        <v>0.9</v>
+      </c>
+      <c r="B14" s="4">
+        <v>6000</v>
+      </c>
+      <c r="C14" s="5">
+        <v>6000</v>
+      </c>
+      <c r="D14" s="5">
+        <v>6000</v>
+      </c>
+      <c r="E14" s="5">
+        <v>6000</v>
+      </c>
+      <c r="F14" s="5">
+        <v>6000</v>
+      </c>
+      <c r="G14" s="5">
+        <v>6000</v>
+      </c>
+      <c r="H14" s="5">
+        <v>6000</v>
+      </c>
+      <c r="I14" s="5">
+        <v>6000</v>
+      </c>
+      <c r="J14" s="5">
+        <v>6000</v>
+      </c>
+      <c r="K14" s="5">
+        <v>6000</v>
+      </c>
+      <c r="L14" s="5">
+        <v>5954</v>
+      </c>
+      <c r="M14" s="9">
+        <v>5625</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="15" customHeight="1">
+      <c r="A15" s="3">
+        <v>1</v>
+      </c>
+      <c r="B15" s="4">
+        <v>6600</v>
+      </c>
+      <c r="C15" s="5">
+        <v>6600</v>
+      </c>
+      <c r="D15" s="5">
+        <v>6600</v>
+      </c>
+      <c r="E15" s="5">
+        <v>6600</v>
+      </c>
+      <c r="F15" s="5">
+        <v>6600</v>
+      </c>
+      <c r="G15" s="5">
+        <v>6600</v>
+      </c>
+      <c r="H15" s="5">
+        <v>6600</v>
+      </c>
+      <c r="I15" s="5">
+        <v>6600</v>
+      </c>
+      <c r="J15" s="5">
+        <v>6600</v>
+      </c>
+      <c r="K15" s="5">
+        <v>6600</v>
+      </c>
+      <c r="L15" s="5">
+        <v>6598</v>
+      </c>
+      <c r="M15" s="9">
+        <v>6450</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="15" customHeight="1">
+      <c r="A16" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B16" s="4">
+        <v>7205</v>
+      </c>
+      <c r="C16" s="5">
+        <v>7205</v>
+      </c>
+      <c r="D16" s="5">
+        <v>7205</v>
+      </c>
+      <c r="E16" s="5">
+        <v>7205</v>
+      </c>
+      <c r="F16" s="5">
+        <v>7205</v>
+      </c>
+      <c r="G16" s="5">
+        <v>7205</v>
+      </c>
+      <c r="H16" s="5">
+        <v>7205</v>
+      </c>
+      <c r="I16" s="5">
+        <v>7205</v>
+      </c>
+      <c r="J16" s="5">
+        <v>7205</v>
+      </c>
+      <c r="K16" s="5">
+        <v>7205</v>
+      </c>
+      <c r="L16" s="5">
+        <v>7205</v>
+      </c>
+      <c r="M16" s="9">
+        <v>7175</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="15" customHeight="1">
+      <c r="A17" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B17" s="6">
+        <v>7800</v>
+      </c>
+      <c r="C17" s="7">
+        <v>7800</v>
+      </c>
+      <c r="D17" s="7">
+        <v>7800</v>
+      </c>
+      <c r="E17" s="7">
+        <v>7800</v>
+      </c>
+      <c r="F17" s="7">
+        <v>7800</v>
+      </c>
+      <c r="G17" s="7">
+        <v>7800</v>
+      </c>
+      <c r="H17" s="7">
+        <v>7800</v>
+      </c>
+      <c r="I17" s="7">
+        <v>7800</v>
+      </c>
+      <c r="J17" s="7">
+        <v>7800</v>
+      </c>
+      <c r="K17" s="7">
+        <v>7800</v>
+      </c>
+      <c r="L17" s="7">
+        <v>7800</v>
+      </c>
+      <c r="M17" s="10">
+        <v>7800</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="23" customWidth="1"/>
+    <col min="2" max="2" width="21" customWidth="1"/>
+    <col min="3" max="3" width="26.5546875" customWidth="1"/>
+    <col min="4" max="4" width="20.6640625" customWidth="1"/>
+    <col min="5" max="5" width="29.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="18">
+      <c r="A1" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="30" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="18">
+      <c r="A2" s="31" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+    </row>
+    <row r="3" spans="1:5" ht="36">
+      <c r="A3" s="31"/>
+      <c r="B3" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="33" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="18">
+      <c r="A4" s="34">
+        <v>0.05</v>
+      </c>
+      <c r="B4" s="35">
+        <v>4.5</v>
+      </c>
+      <c r="C4" s="35">
+        <v>4.5</v>
+      </c>
+      <c r="D4" s="35">
+        <v>4.5</v>
+      </c>
+      <c r="E4" s="35">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="18">
+      <c r="A5" s="36">
+        <v>0.1</v>
+      </c>
+      <c r="B5" s="35">
+        <v>9</v>
+      </c>
+      <c r="C5" s="35">
+        <v>9</v>
+      </c>
+      <c r="D5" s="35">
+        <v>9</v>
+      </c>
+      <c r="E5" s="35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="18">
+      <c r="A6" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="B6" s="35">
+        <v>13.5</v>
+      </c>
+      <c r="C6" s="35">
+        <v>13.5</v>
+      </c>
+      <c r="D6" s="35">
+        <v>13.5</v>
+      </c>
+      <c r="E6" s="35">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="18">
+      <c r="A7" s="36">
+        <v>0.3</v>
+      </c>
+      <c r="B7" s="35">
+        <v>18</v>
+      </c>
+      <c r="C7" s="35">
+        <v>18</v>
+      </c>
+      <c r="D7" s="35">
+        <v>18</v>
+      </c>
+      <c r="E7" s="35">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="18">
+      <c r="A8" s="36">
+        <v>0.4</v>
+      </c>
+      <c r="B8" s="35">
+        <v>28</v>
+      </c>
+      <c r="C8" s="35">
+        <v>28</v>
+      </c>
+      <c r="D8" s="35">
+        <v>28</v>
+      </c>
+      <c r="E8" s="35">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="18">
+      <c r="A9" s="36">
+        <v>0.5</v>
+      </c>
+      <c r="B9" s="35">
+        <v>34</v>
+      </c>
+      <c r="C9" s="35">
+        <v>34</v>
+      </c>
+      <c r="D9" s="35">
+        <v>34</v>
+      </c>
+      <c r="E9" s="35">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="18">
+      <c r="A10" s="36">
+        <v>0.6</v>
+      </c>
+      <c r="B10" s="35">
+        <v>40</v>
+      </c>
+      <c r="C10" s="35">
+        <v>40</v>
+      </c>
+      <c r="D10" s="35">
+        <v>40</v>
+      </c>
+      <c r="E10" s="35">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="18">
+      <c r="A11" s="36">
+        <v>0.7</v>
+      </c>
+      <c r="B11" s="35">
+        <v>43</v>
+      </c>
+      <c r="C11" s="35">
+        <v>43</v>
+      </c>
+      <c r="D11" s="35">
+        <v>43</v>
+      </c>
+      <c r="E11" s="35">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="18">
+      <c r="A12" s="36">
+        <v>0.8</v>
+      </c>
+      <c r="B12" s="35">
+        <v>46</v>
+      </c>
+      <c r="C12" s="35">
+        <v>46</v>
+      </c>
+      <c r="D12" s="35">
+        <v>46</v>
+      </c>
+      <c r="E12" s="35">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="18">
+      <c r="A13" s="36">
+        <v>0.9</v>
+      </c>
+      <c r="B13" s="35">
+        <v>52</v>
+      </c>
+      <c r="C13" s="35">
+        <v>52</v>
+      </c>
+      <c r="D13" s="35">
+        <v>52</v>
+      </c>
+      <c r="E13" s="35">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="18">
+      <c r="A14" s="36">
+        <v>1</v>
+      </c>
+      <c r="B14" s="35">
+        <v>58</v>
+      </c>
+      <c r="C14" s="35">
+        <v>58</v>
+      </c>
+      <c r="D14" s="35">
+        <v>58</v>
+      </c>
+      <c r="E14" s="35">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="18">
+      <c r="A15" s="36">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B15" s="35">
+        <v>66</v>
+      </c>
+      <c r="C15" s="35">
+        <v>66</v>
+      </c>
+      <c r="D15" s="35">
+        <v>66</v>
+      </c>
+      <c r="E15" s="35">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="18">
+      <c r="A16" s="36">
+        <v>1.2</v>
+      </c>
+      <c r="B16" s="35">
+        <v>70</v>
+      </c>
+      <c r="C16" s="35">
+        <v>70</v>
+      </c>
+      <c r="D16" s="35">
+        <v>70</v>
+      </c>
+      <c r="E16" s="35">
+        <v>70</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:E2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>